--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0003T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.88258208826074</v>
+        <v>4.20591958934237</v>
       </c>
       <c r="D2" t="n">
-        <v>26.46887060512993</v>
+        <v>4.301191473333613</v>
       </c>
       <c r="E2" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F2" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.40487119409911</v>
+        <v>1.690791569041105</v>
       </c>
       <c r="D3" t="n">
-        <v>10.81979518154715</v>
+        <v>1.758216717001412</v>
       </c>
       <c r="E3" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F3" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.51204037486137</v>
+        <v>4.795706560914973</v>
       </c>
       <c r="D4" t="n">
-        <v>31.07689587845497</v>
+        <v>5.049995580248932</v>
       </c>
       <c r="E4" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F4" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.40141605839906</v>
+        <v>6.077730109489847</v>
       </c>
       <c r="D5" t="n">
-        <v>36.73099599591102</v>
+        <v>5.968786849335541</v>
       </c>
       <c r="E5" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F5" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.02194824974243</v>
+        <v>2.441066590583145</v>
       </c>
       <c r="D6" t="n">
-        <v>16.8775214689394</v>
+        <v>2.742597238702652</v>
       </c>
       <c r="E6" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F6" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.666156899658566</v>
+        <v>0.9207504961945171</v>
       </c>
       <c r="D7" t="n">
-        <v>7.247327279715979</v>
+        <v>1.177690682953846</v>
       </c>
       <c r="E7" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F7" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>2.445007007508057</v>
+        <v>0.3973136387200593</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5938139170053192</v>
+        <v>0.09649476151336436</v>
       </c>
       <c r="E8" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F8" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.82501013588832</v>
+        <v>1.759064147081852</v>
       </c>
       <c r="D9" t="n">
-        <v>10.60058409994592</v>
+        <v>1.722594916241212</v>
       </c>
       <c r="E9" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F9" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.59249439836428</v>
+        <v>2.858780339734196</v>
       </c>
       <c r="D10" t="n">
-        <v>18.2784170406075</v>
+        <v>2.97024276909872</v>
       </c>
       <c r="E10" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F10" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>63.14527099381938</v>
+        <v>10.26110653649565</v>
       </c>
       <c r="D11" t="n">
-        <v>61.31225098043995</v>
+        <v>9.963240784321492</v>
       </c>
       <c r="E11" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F11" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.90291257680627</v>
+        <v>4.046723293731019</v>
       </c>
       <c r="D12" t="n">
-        <v>18.33594341656846</v>
+        <v>2.979590805192375</v>
       </c>
       <c r="E12" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F12" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>14.51651287337207</v>
+        <v>2.358933341922962</v>
       </c>
       <c r="D13" t="n">
-        <v>19.3112365372629</v>
+        <v>3.138075937305222</v>
       </c>
       <c r="E13" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F13" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>61.44253537872953</v>
+        <v>9.98441199904355</v>
       </c>
       <c r="D14" t="n">
-        <v>62.46911906024589</v>
+        <v>10.15123184728996</v>
       </c>
       <c r="E14" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F14" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>36.9988706083915</v>
+        <v>6.012316473863619</v>
       </c>
       <c r="D15" t="n">
-        <v>38.04718477992732</v>
+        <v>6.182667526738189</v>
       </c>
       <c r="E15" t="n">
-        <v>18.24530582778825</v>
+        <v>2.964862197015592</v>
       </c>
       <c r="F15" t="n">
-        <v>18.07098103642723</v>
+        <v>2.936534418419426</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
